--- a/Unity/Assets/Config/Excel/JiaYuanPastureConfig.xlsx
+++ b/Unity/Assets/Config/Excel/JiaYuanPastureConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="21495" windowHeight="12045"/>
   </bookViews>
   <sheets>
     <sheet name="JiaYuanPastureProto" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
     <author>作者</author>
   </authors>
   <commentList>
-    <comment ref="G3" authorId="0">
+    <comment ref="F3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -87,7 +87,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L3" authorId="0">
+    <comment ref="K3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -114,11 +114,74 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="76">
+  <si>
+    <t>##var</t>
+  </si>
   <si>
     <t>Id</t>
   </si>
   <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Lv</t>
+  </si>
+  <si>
+    <t>Assets</t>
+  </si>
+  <si>
+    <t>UpTime</t>
+  </si>
+  <si>
+    <t>PeopleNum</t>
+  </si>
+  <si>
+    <t>BuyGold</t>
+  </si>
+  <si>
+    <t>SellGold</t>
+  </si>
+  <si>
+    <t>DropTime</t>
+  </si>
+  <si>
+    <t>GetPro</t>
+  </si>
+  <si>
+    <t>GetItemID</t>
+  </si>
+  <si>
+    <t>Speak</t>
+  </si>
+  <si>
+    <t>Des</t>
+  </si>
+  <si>
+    <t>BuyJiaYuanLv</t>
+  </si>
+  <si>
+    <t>BuyJiaYuanPro</t>
+  </si>
+  <si>
+    <t>##type</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>(array#sep=,),int</t>
+  </si>
+  <si>
+    <t>double</t>
+  </si>
+  <si>
+    <t>##</t>
+  </si>
+  <si>
     <t>名称</t>
   </si>
   <si>
@@ -156,60 +219,6 @@
   </si>
   <si>
     <t>购买家园权重</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Lv</t>
-  </si>
-  <si>
-    <t>Assets</t>
-  </si>
-  <si>
-    <t>UpTime</t>
-  </si>
-  <si>
-    <t>PeopleNum</t>
-  </si>
-  <si>
-    <t>BuyGold</t>
-  </si>
-  <si>
-    <t>SellGold</t>
-  </si>
-  <si>
-    <t>DropTime</t>
-  </si>
-  <si>
-    <t>GetPro</t>
-  </si>
-  <si>
-    <t>GetItemID</t>
-  </si>
-  <si>
-    <t>Speak</t>
-  </si>
-  <si>
-    <t>Des</t>
-  </si>
-  <si>
-    <t>BuyJiaYuanLv</t>
-  </si>
-  <si>
-    <t>BuyJiaYuanPro</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>int[]</t>
-  </si>
-  <si>
-    <t>double</t>
   </si>
   <si>
     <t>鸡</t>
@@ -345,7 +354,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -353,7 +362,7 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
@@ -531,19 +540,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Tahoma"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
@@ -560,7 +556,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="50">
+  <fills count="43">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -810,48 +806,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799951170384838"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -871,9 +825,7 @@
       <right style="thin">
         <color theme="0"/>
       </right>
-      <top style="thin">
-        <color theme="0"/>
-      </top>
+      <top/>
       <bottom/>
       <diagonal/>
     </border>
@@ -899,7 +851,9 @@
       <right style="thin">
         <color theme="0"/>
       </right>
-      <top/>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -1191,950 +1145,952 @@
     <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="49" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="49" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="49" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="49" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="49" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="49" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="49" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="49" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="49" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="49" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="49" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="49" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="49" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="49" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="49" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="49" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="49" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="49" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="49" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="49" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="342" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="342" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="342" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2544,7 +2500,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2">
-    <tableStyle name="MySqlDefault" count="2" xr9:uid="{86D8F346-E4FE-4C61-BA33-4B656AC1290A}">
+    <tableStyle name="MySqlDefault" count="2" xr9:uid="{089E9207-63BB-40A3-A605-E98E7B054921}">
       <tableStyleElement type="wholeTable" dxfId="1"/>
       <tableStyleElement type="headerRow" dxfId="0"/>
     </tableStyle>
@@ -2844,843 +2800,845 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:Q24"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="6" width="17.875" customWidth="1"/>
-    <col min="7" max="7" width="25.75" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="14" width="16.75" customWidth="1"/>
-    <col min="15" max="15" width="16" customWidth="1"/>
-    <col min="16" max="17" width="14" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="5" width="17.875" customWidth="1"/>
+    <col min="6" max="6" width="25.75" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="8" max="13" width="16.75" customWidth="1"/>
+    <col min="14" max="14" width="16" customWidth="1"/>
+    <col min="15" max="16" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="20.1" customHeight="1" spans="7:13">
-      <c r="G1"/>
-      <c r="I1"/>
-      <c r="J1"/>
-      <c r="M1"/>
+    <row r="1" customFormat="1" ht="20.1" customHeight="1" spans="1:16">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="2" ht="20.1" customHeight="1"/>
-    <row r="3" ht="20.1" customHeight="1" spans="3:17">
-      <c r="C3" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="3" t="s">
+    <row r="2" customFormat="1" ht="20.1" customHeight="1" spans="1:16">
+      <c r="A2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" ht="20.1" customHeight="1" spans="1:16">
+      <c r="A3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
+      <c r="C3" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>23</v>
+      </c>
       <c r="E3" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="O3" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="P3" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" ht="20.1" customHeight="1" spans="2:16">
+      <c r="B4" s="6">
+        <v>10001</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="8">
+        <v>1</v>
+      </c>
+      <c r="E4" s="6">
+        <v>10001</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="G4" s="7">
+        <v>1</v>
+      </c>
+      <c r="H4" s="7">
+        <v>900</v>
+      </c>
+      <c r="I4" s="7">
+        <f>H4/2</f>
+        <v>450</v>
+      </c>
+      <c r="J4" s="7">
+        <v>2160</v>
+      </c>
+      <c r="K4" s="7">
+        <v>0.25</v>
+      </c>
+      <c r="L4" s="10">
+        <v>10035001</v>
+      </c>
+      <c r="M4" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="N4" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="O4" s="7">
+        <v>1</v>
+      </c>
+      <c r="P4" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" ht="20.1" customHeight="1" spans="2:16">
+      <c r="B5" s="6">
+        <v>10002</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" s="8">
         <v>2</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="E5" s="6">
+        <v>10001</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5" s="7">
+        <v>1</v>
+      </c>
+      <c r="H5" s="7">
+        <v>1350</v>
+      </c>
+      <c r="I5" s="7">
+        <f t="shared" ref="I5:I17" si="0">H5/2</f>
+        <v>675</v>
+      </c>
+      <c r="J5" s="7">
+        <v>2700</v>
+      </c>
+      <c r="K5" s="7">
+        <v>0.25</v>
+      </c>
+      <c r="L5" s="10">
+        <v>10035002</v>
+      </c>
+      <c r="M5" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="N5" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="O5" s="7">
+        <v>2</v>
+      </c>
+      <c r="P5" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" ht="20.1" customHeight="1" spans="2:16">
+      <c r="B6" s="6">
+        <v>10003</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" s="8">
         <v>3</v>
       </c>
-      <c r="G3" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="O3" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="P3" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q3" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" ht="20.1" customHeight="1" spans="3:17">
-      <c r="C4" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="M4" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="O4" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="P4" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q4" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" ht="20.1" customHeight="1" spans="3:17">
-      <c r="C5" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="M5" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="N5" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="O5" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="P5" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q5" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" ht="20.1" customHeight="1" spans="3:17">
-      <c r="C6" s="6">
+      <c r="E6" s="6">
         <v>10001</v>
       </c>
-      <c r="D6" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="E6" s="8">
+      <c r="F6" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="G6" s="7">
         <v>1</v>
       </c>
-      <c r="F6" s="6">
-        <v>10001</v>
-      </c>
-      <c r="G6" s="11" t="s">
-        <v>33</v>
-      </c>
       <c r="H6" s="7">
-        <v>1</v>
+        <v>1800</v>
       </c>
       <c r="I6" s="7">
-        <v>900</v>
-      </c>
-      <c r="J6" s="7">
-        <f>I6/2</f>
-        <v>450</v>
-      </c>
-      <c r="K6" s="7">
-        <v>2160</v>
-      </c>
-      <c r="L6" s="7">
-        <v>0.25</v>
-      </c>
-      <c r="M6" s="10">
-        <v>10035001</v>
-      </c>
-      <c r="N6" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="O6" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="P6" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q6" s="7">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" ht="20.1" customHeight="1" spans="3:17">
-      <c r="C7" s="6">
-        <v>10002</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="E7" s="8">
-        <v>2</v>
-      </c>
-      <c r="F7" s="6">
-        <v>10001</v>
-      </c>
-      <c r="G7" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="H7" s="7">
-        <v>1</v>
-      </c>
-      <c r="I7" s="7">
-        <v>1350</v>
-      </c>
-      <c r="J7" s="7">
-        <f t="shared" ref="J7:J19" si="0">I7/2</f>
-        <v>675</v>
-      </c>
-      <c r="K7" s="7">
-        <v>2700</v>
-      </c>
-      <c r="L7" s="7">
-        <v>0.25</v>
-      </c>
-      <c r="M7" s="10">
-        <v>10035002</v>
-      </c>
-      <c r="N7" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="O7" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="P7" s="7">
-        <v>2</v>
-      </c>
-      <c r="Q7" s="7">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="8" ht="20.1" customHeight="1" spans="3:17">
-      <c r="C8" s="6">
-        <v>10003</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="E8" s="8">
-        <v>3</v>
-      </c>
-      <c r="F8" s="6">
-        <v>10001</v>
-      </c>
-      <c r="G8" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="H8" s="7">
-        <v>1</v>
-      </c>
-      <c r="I8" s="7">
-        <v>1800</v>
-      </c>
-      <c r="J8" s="7">
         <f t="shared" si="0"/>
         <v>900</v>
       </c>
-      <c r="K8" s="7">
+      <c r="J6" s="7">
         <v>3240</v>
       </c>
-      <c r="L8" s="7">
+      <c r="K6" s="7">
         <v>0.25</v>
       </c>
-      <c r="M8" s="10">
+      <c r="L6" s="10">
         <v>10035003</v>
       </c>
-      <c r="N8" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="O8" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="P8" s="7">
+      <c r="M6" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="N6" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="O6" s="7">
         <v>3</v>
       </c>
-      <c r="Q8" s="7">
+      <c r="P6" s="7">
         <v>100</v>
       </c>
     </row>
-    <row r="9" ht="20.1" customHeight="1" spans="3:17">
-      <c r="C9" s="6">
+    <row r="7" ht="20.1" customHeight="1" spans="2:16">
+      <c r="B7" s="6">
         <v>10004</v>
       </c>
-      <c r="D9" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="E9" s="8">
+      <c r="C7" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" s="8">
         <v>4</v>
       </c>
-      <c r="F9" s="6">
+      <c r="E7" s="6">
         <v>10001</v>
       </c>
-      <c r="G9" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="H9" s="7">
+      <c r="F7" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="G7" s="7">
         <v>2</v>
       </c>
-      <c r="I9" s="7">
+      <c r="H7" s="7">
         <v>4500</v>
       </c>
-      <c r="J9" s="7">
+      <c r="I7" s="7">
         <f t="shared" si="0"/>
         <v>2250</v>
       </c>
-      <c r="K9" s="7">
+      <c r="J7" s="7">
         <v>3780</v>
       </c>
-      <c r="L9" s="7">
+      <c r="K7" s="7">
         <v>0.25</v>
       </c>
-      <c r="M9" s="10">
+      <c r="L7" s="10">
         <v>10035004</v>
       </c>
-      <c r="N9" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="O9" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="P9" s="7">
+      <c r="M7" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="N7" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="O7" s="7">
         <v>5</v>
       </c>
-      <c r="Q9" s="7">
+      <c r="P7" s="7">
         <v>100</v>
       </c>
     </row>
-    <row r="10" ht="20.1" customHeight="1" spans="3:17">
-      <c r="C10" s="6">
+    <row r="8" ht="20.1" customHeight="1" spans="2:16">
+      <c r="B8" s="6">
         <v>10005</v>
       </c>
-      <c r="D10" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="E10" s="8">
+      <c r="C8" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" s="8">
         <v>5</v>
       </c>
-      <c r="F10" s="6">
+      <c r="E8" s="6">
         <v>10001</v>
       </c>
-      <c r="G10" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="H10" s="7">
+      <c r="F8" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="G8" s="7">
         <v>2</v>
       </c>
-      <c r="I10" s="7">
+      <c r="H8" s="7">
         <v>5400</v>
       </c>
-      <c r="J10" s="7">
+      <c r="I8" s="7">
         <f t="shared" si="0"/>
         <v>2700</v>
       </c>
-      <c r="K10" s="7">
+      <c r="J8" s="7">
         <v>4320</v>
       </c>
-      <c r="L10" s="7">
+      <c r="K8" s="7">
         <v>0.25</v>
       </c>
-      <c r="M10" s="10">
+      <c r="L8" s="10">
         <v>10035005</v>
       </c>
-      <c r="N10" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="O10" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="P10" s="7">
+      <c r="M8" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="N8" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="O8" s="7">
         <v>7</v>
       </c>
-      <c r="Q10" s="7">
+      <c r="P8" s="7">
         <v>100</v>
       </c>
     </row>
-    <row r="11" ht="20.1" customHeight="1" spans="3:17">
-      <c r="C11" s="6">
+    <row r="9" ht="20.1" customHeight="1" spans="2:16">
+      <c r="B9" s="6">
         <v>10006</v>
       </c>
-      <c r="D11" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="E11" s="8">
+      <c r="C9" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D9" s="8">
         <v>6</v>
       </c>
-      <c r="F11" s="6">
+      <c r="E9" s="6">
         <v>10001</v>
       </c>
-      <c r="G11" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="H11" s="7">
+      <c r="F9" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="G9" s="7">
         <v>2</v>
       </c>
-      <c r="I11" s="7">
+      <c r="H9" s="7">
         <v>6000</v>
       </c>
-      <c r="J11" s="7">
+      <c r="I9" s="7">
         <f t="shared" si="0"/>
         <v>3000</v>
       </c>
-      <c r="K11" s="7">
+      <c r="J9" s="7">
         <v>4860</v>
       </c>
-      <c r="L11" s="7">
+      <c r="K9" s="7">
         <v>0.25</v>
       </c>
-      <c r="M11" s="10">
+      <c r="L9" s="10">
         <v>10035006</v>
       </c>
-      <c r="N11" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="O11" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="P11" s="7">
+      <c r="M9" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="N9" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="O9" s="7">
         <v>9</v>
       </c>
-      <c r="Q11" s="7">
+      <c r="P9" s="7">
         <v>100</v>
       </c>
     </row>
-    <row r="12" ht="20.1" customHeight="1" spans="3:17">
-      <c r="C12" s="6">
+    <row r="10" ht="20.1" customHeight="1" spans="2:16">
+      <c r="B10" s="6">
         <v>10007</v>
       </c>
-      <c r="D12" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="E12" s="8">
+      <c r="C10" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" s="8">
         <v>7</v>
       </c>
-      <c r="F12" s="6">
+      <c r="E10" s="6">
         <v>10001</v>
       </c>
-      <c r="G12" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="H12" s="7">
+      <c r="F10" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="G10" s="7">
         <v>3</v>
       </c>
-      <c r="I12" s="7">
+      <c r="H10" s="7">
         <v>10350</v>
       </c>
-      <c r="J12" s="7">
+      <c r="I10" s="7">
         <f t="shared" si="0"/>
         <v>5175</v>
       </c>
-      <c r="K12" s="7">
+      <c r="J10" s="7">
         <v>5400</v>
       </c>
-      <c r="L12" s="7">
+      <c r="K10" s="7">
         <v>0.25</v>
       </c>
-      <c r="M12" s="10">
+      <c r="L10" s="10">
         <v>10035007</v>
       </c>
-      <c r="N12" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="O12" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="P12" s="7">
+      <c r="M10" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="N10" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="O10" s="7">
         <v>11</v>
       </c>
-      <c r="Q12" s="7">
+      <c r="P10" s="7">
         <v>100</v>
       </c>
     </row>
-    <row r="13" ht="20.1" customHeight="1" spans="3:17">
-      <c r="C13" s="6">
+    <row r="11" ht="20.1" customHeight="1" spans="2:16">
+      <c r="B11" s="6">
         <v>10008</v>
       </c>
-      <c r="D13" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="E13" s="8">
+      <c r="C11" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D11" s="8">
         <v>8</v>
       </c>
-      <c r="F13" s="6">
+      <c r="E11" s="6">
         <v>10001</v>
       </c>
-      <c r="G13" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="H13" s="7">
+      <c r="F11" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="G11" s="7">
         <v>3</v>
       </c>
-      <c r="I13" s="7">
+      <c r="H11" s="7">
         <v>11700</v>
       </c>
-      <c r="J13" s="7">
+      <c r="I11" s="7">
         <f t="shared" si="0"/>
         <v>5850</v>
       </c>
-      <c r="K13" s="7">
+      <c r="J11" s="7">
         <v>5940</v>
       </c>
-      <c r="L13" s="7">
+      <c r="K11" s="7">
         <v>0.25</v>
       </c>
-      <c r="M13" s="10">
+      <c r="L11" s="10">
         <v>10035008</v>
       </c>
-      <c r="N13" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="O13" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="P13" s="7">
+      <c r="M11" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="N11" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="O11" s="7">
         <v>13</v>
       </c>
-      <c r="Q13" s="7">
+      <c r="P11" s="7">
         <v>100</v>
       </c>
     </row>
-    <row r="14" ht="20.1" customHeight="1" spans="3:17">
-      <c r="C14" s="6">
+    <row r="12" ht="20.1" customHeight="1" spans="2:16">
+      <c r="B12" s="6">
         <v>10009</v>
       </c>
-      <c r="D14" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="E14" s="8">
+      <c r="C12" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="D12" s="8">
         <v>9</v>
       </c>
-      <c r="F14" s="6">
+      <c r="E12" s="6">
         <v>10001</v>
       </c>
-      <c r="G14" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="H14" s="7">
+      <c r="F12" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="G12" s="7">
         <v>3</v>
       </c>
-      <c r="I14" s="7">
+      <c r="H12" s="7">
         <v>13500</v>
       </c>
-      <c r="J14" s="7">
+      <c r="I12" s="7">
         <f t="shared" si="0"/>
         <v>6750</v>
       </c>
-      <c r="K14" s="7">
+      <c r="J12" s="7">
         <v>5940</v>
       </c>
-      <c r="L14" s="7">
+      <c r="K12" s="7">
         <v>0.25</v>
       </c>
-      <c r="M14" s="10">
+      <c r="L12" s="10">
         <v>10035009</v>
       </c>
-      <c r="N14" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="O14" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="P14" s="7">
+      <c r="M12" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="N12" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="O12" s="7">
         <v>15</v>
       </c>
-      <c r="Q14" s="7">
+      <c r="P12" s="7">
         <v>100</v>
       </c>
     </row>
-    <row r="15" ht="20.1" customHeight="1" spans="3:17">
-      <c r="C15" s="6">
+    <row r="13" ht="20.1" customHeight="1" spans="2:16">
+      <c r="B13" s="6">
         <v>10010</v>
       </c>
-      <c r="D15" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="E15" s="8">
+      <c r="C13" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13" s="8">
         <v>10</v>
       </c>
-      <c r="F15" s="6">
+      <c r="E13" s="6">
         <v>10001</v>
       </c>
-      <c r="G15" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="H15" s="7">
+      <c r="F13" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="G13" s="7">
         <v>3</v>
       </c>
-      <c r="I15" s="7">
+      <c r="H13" s="7">
         <v>15300</v>
       </c>
-      <c r="J15" s="7">
+      <c r="I13" s="7">
         <f t="shared" si="0"/>
         <v>7650</v>
       </c>
-      <c r="K15" s="7">
+      <c r="J13" s="7">
         <v>6480</v>
       </c>
-      <c r="L15" s="7">
+      <c r="K13" s="7">
         <v>0.25</v>
       </c>
-      <c r="M15" s="10">
+      <c r="L13" s="10">
         <v>10035010</v>
       </c>
-      <c r="N15" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="O15" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="P15" s="7">
+      <c r="M13" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="N13" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="O13" s="7">
         <v>17</v>
       </c>
-      <c r="Q15" s="7">
+      <c r="P13" s="7">
         <v>100</v>
       </c>
     </row>
-    <row r="16" ht="20.1" customHeight="1" spans="3:17">
-      <c r="C16" s="6">
+    <row r="14" ht="20.1" customHeight="1" spans="2:16">
+      <c r="B14" s="6">
         <v>10011</v>
       </c>
-      <c r="D16" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="E16" s="8">
+      <c r="C14" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="D14" s="8">
         <v>11</v>
       </c>
-      <c r="F16" s="6">
+      <c r="E14" s="6">
         <v>10001</v>
       </c>
-      <c r="G16" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="H16" s="7">
+      <c r="F14" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="G14" s="7">
         <v>4</v>
       </c>
-      <c r="I16" s="7">
+      <c r="H14" s="7">
         <v>22800</v>
       </c>
-      <c r="J16" s="7">
+      <c r="I14" s="7">
         <f t="shared" si="0"/>
         <v>11400</v>
       </c>
-      <c r="K16" s="7">
+      <c r="J14" s="7">
         <v>6480</v>
       </c>
-      <c r="L16" s="7">
+      <c r="K14" s="7">
         <v>0.25</v>
       </c>
-      <c r="M16" s="10">
+      <c r="L14" s="10">
         <v>10035011</v>
       </c>
-      <c r="N16" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="O16" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="P16" s="7">
+      <c r="M14" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="N14" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="O14" s="7">
         <v>19</v>
       </c>
-      <c r="Q16" s="7">
+      <c r="P14" s="7">
         <v>100</v>
       </c>
     </row>
-    <row r="17" ht="20.1" customHeight="1" spans="3:17">
-      <c r="C17" s="6">
+    <row r="15" ht="20.1" customHeight="1" spans="2:16">
+      <c r="B15" s="6">
         <v>10012</v>
       </c>
-      <c r="D17" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="E17" s="8">
+      <c r="C15" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="D15" s="8">
         <v>12</v>
       </c>
-      <c r="F17" s="6">
+      <c r="E15" s="6">
         <v>10001</v>
       </c>
-      <c r="G17" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="H17" s="7">
+      <c r="F15" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="G15" s="7">
         <v>4</v>
       </c>
-      <c r="I17" s="7">
+      <c r="H15" s="7">
         <v>25200</v>
       </c>
-      <c r="J17" s="7">
+      <c r="I15" s="7">
         <f t="shared" si="0"/>
         <v>12600</v>
       </c>
-      <c r="K17" s="7">
+      <c r="J15" s="7">
         <v>7020</v>
       </c>
-      <c r="L17" s="7">
+      <c r="K15" s="7">
         <v>0.25</v>
       </c>
-      <c r="M17" s="10">
+      <c r="L15" s="10">
         <v>10035012</v>
       </c>
-      <c r="N17" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="O17" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="P17" s="7">
+      <c r="M15" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="N15" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="O15" s="7">
         <v>21</v>
       </c>
-      <c r="Q17" s="7">
+      <c r="P15" s="7">
         <v>100</v>
       </c>
     </row>
-    <row r="18" ht="20.1" customHeight="1" spans="3:17">
-      <c r="C18" s="6">
+    <row r="16" ht="20.1" customHeight="1" spans="2:16">
+      <c r="B16" s="6">
         <v>10013</v>
       </c>
-      <c r="D18" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="E18" s="8">
+      <c r="C16" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="D16" s="8">
         <v>13</v>
       </c>
-      <c r="F18" s="6">
+      <c r="E16" s="6">
         <v>10001</v>
       </c>
-      <c r="G18" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="H18" s="7">
+      <c r="F16" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="G16" s="7">
         <v>4</v>
       </c>
-      <c r="I18" s="7">
+      <c r="H16" s="7">
         <v>27600</v>
       </c>
-      <c r="J18" s="7">
+      <c r="I16" s="7">
         <f t="shared" si="0"/>
         <v>13800</v>
       </c>
-      <c r="K18" s="7">
+      <c r="J16" s="7">
         <v>7560</v>
       </c>
-      <c r="L18" s="7">
+      <c r="K16" s="7">
         <v>0.25</v>
       </c>
-      <c r="M18" s="10">
+      <c r="L16" s="10">
         <v>10035013</v>
       </c>
-      <c r="N18" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="O18" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="P18" s="7">
+      <c r="M16" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="N16" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="O16" s="7">
         <v>23</v>
       </c>
-      <c r="Q18" s="7">
+      <c r="P16" s="7">
         <v>100</v>
       </c>
     </row>
-    <row r="19" ht="20.1" customHeight="1" spans="3:17">
-      <c r="C19" s="6">
+    <row r="17" ht="20.1" customHeight="1" spans="2:16">
+      <c r="B17" s="6">
         <v>10014</v>
       </c>
-      <c r="D19" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="E19" s="8">
+      <c r="C17" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="D17" s="8">
         <v>14</v>
       </c>
-      <c r="F19" s="6">
+      <c r="E17" s="6">
         <v>10001</v>
       </c>
-      <c r="G19" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="H19" s="7">
+      <c r="F17" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="G17" s="7">
         <v>4</v>
       </c>
-      <c r="I19" s="7">
+      <c r="H17" s="7">
         <v>30000</v>
       </c>
-      <c r="J19" s="7">
+      <c r="I17" s="7">
         <f t="shared" si="0"/>
         <v>15000</v>
       </c>
-      <c r="K19" s="7">
+      <c r="J17" s="7">
         <v>8100</v>
       </c>
-      <c r="L19" s="7">
+      <c r="K17" s="7">
         <v>0.25</v>
       </c>
-      <c r="M19" s="10">
+      <c r="L17" s="10">
         <v>10035014</v>
       </c>
-      <c r="N19" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="O19" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="P19" s="7">
+      <c r="M17" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="N17" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="O17" s="7">
         <v>25</v>
       </c>
-      <c r="Q19" s="7">
+      <c r="P17" s="7">
         <v>100</v>
       </c>
     </row>
+    <row r="18" ht="20.1" customHeight="1"/>
+    <row r="19" ht="20.1" customHeight="1"/>
     <row r="20" ht="20.1" customHeight="1"/>
     <row r="21" ht="20.1" customHeight="1"/>
     <row r="22" ht="20.1" customHeight="1"/>
-    <row r="23" ht="20.1" customHeight="1"/>
-    <row r="24" ht="20.1" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
